--- a/Для сайта/ЭТО/frame.xlsx
+++ b/Для сайта/ЭТО/frame.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Projects\380-25_Ivanovo_TEC\Для сайта\ЭТО\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B4B2FE-7DCB-496D-B5DC-589D3FA247D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6FC0CF-67C6-4741-98B7-E315690C4B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -85,13 +85,13 @@
     <t>РФ, Ивановская область, г.Иваново, ул. Суворова, 76</t>
   </si>
   <si>
-    <t>260</t>
-  </si>
-  <si>
     <t>878.2023-АСУ ТП.СБ.1</t>
   </si>
   <si>
     <t>07.25</t>
+  </si>
+  <si>
+    <t>278</t>
   </si>
 </sst>
 </file>
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -524,13 +524,13 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
